--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -5426,10 +5426,14 @@
       <c r="K74" s="6" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="M74" s="6" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>Done overnight; smoke-tested headless.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -5544,10 +5548,14 @@
       <c r="K76" s="6" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="M76" s="6" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>Done overnight (src/interactions.ts); wave path needs a real-headset check.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -5599,10 +5607,14 @@
       <c r="K77" s="6" t="inlineStr"/>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="M77" s="6" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>Done overnight (src/fade.ts); every teleport now fades. XR quad path needs a headset check.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -5780,10 +5792,14 @@
       <c r="K80" s="6" t="inlineStr"/>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="M80" s="6" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>Done overnight (src/audio.ts); SFX currently 2D — positional attach is a follow-up once real assets land.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -5839,10 +5855,14 @@
       <c r="K81" s="6" t="inlineStr"/>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="M81" s="6" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>Done overnight.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -5898,10 +5918,14 @@
       <c r="K82" s="6" t="inlineStr"/>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="M82" s="6" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>Done overnight (src/companion.ts); billboard live, rigged adapter pending avatar asset.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -5453,7 +5453,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Backend system_prompt.txt paste (avatar-chat repo)</t>
+          <t>Backend companion mode: deploy to live system_prompt.txt (avatar-chat)</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC A — paste-ready block: ---TELEPORT:&lt;sceneId&gt;--- marker (BEFORE any ---LINKS---) + companion brevity/guardrails (RAG-grounded, no politics/current events/off-topic, 1-3 spoken sentences). Curl test after restart.</t>
+          <t>PREPARED on avatar-chat branch claude/webxr-companion-prompt: template section (surface-gated so jeffxr.com/chat is untouched), scene_context cap 200-&gt;600 in main.py, 2D marker strip in chat-block.html. Jeff on the Spark: merge branch, copy new section into gitignored system_prompt.txt (keep DYNAMICALLY ADDED KNOWLEDGE), restart jeff-avatar.service, curl test.</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Cats: names, coat colors, one reference photo each</t>
+          <t>RESOLVED — Cats: Pumpkin (orange tabby), Pepper (gray tabby), Poppy (marbled orange/gray/white tabby); photos in planning/reference/cats/</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -897,12 +897,12 @@
       <c r="K3" s="6" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>NEEDS JEFF</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>Blocks 3 Tripo cat props + possibly S5 reveal image.</t>
+          <t>Was blocking 3 Tripo cat props — now unblocked. Cast: Pepper sleeps in S1, Poppy watches the S2 screen, Pumpkin is the S3 hologram.</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>World builder votes cats.</t>
+          <t>World builder votes cats. NEW candidate: the JB Proxie + all-three-cats render (planning/reference/cats/jb-proxie-with-all-three-cats.jpg) — already stylized, Matrix-green sunglasses fit Lightworks; needs grayscale conversion.</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Cat #1 (sleeping)</t>
+          <t>Cat: Pepper, asleep on a crate</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Tripo</t>
+          <t>Tripo (image-conditioned)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>sleeping cat curled up, short fur, low poly, game ready</t>
+          <t>sleeping gray tabby cat curled up in a tight ball, silver-gray coat with dark charcoal stripes, short fur, game ready</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Cat decision</t>
+          <t>World gen S1</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>BLOCKED on cat decision (names/colors/photos)</t>
+          <t>Image: planning/reference/cats/pepper-gray-tabby-sleeping.jpg (exact pose!); pepper-gray-tabby-alert.jpg for markings</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Cat #2 (watching screen)</t>
+          <t>Cat: Poppy, watching the island game</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Tripo</t>
+          <t>Tripo (image-conditioned)</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>cat sitting upright on a desk looking at a screen, short fur, low poly, game ready</t>
+          <t>cat sitting upright on a desk looking at a screen, marbled tabby with soft orange gray and white patches, white chest and front paws, short fur, game ready</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Cat decision</t>
+          <t>World gen S2</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>BLOCKED on cat decision</t>
+          <t>Image: planning/reference/cats/poppy-marbled-tabby-sitting.jpg (exact pose)</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Holo-cat #3 (wireframe patrol)</t>
+          <t>Holo-cat: Pumpkin, wireframe patrol</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>low poly cat walking, game ready</t>
+          <t>low poly chunky orange tabby cat walking, rounded belly, game ready</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>Cat decision</t>
+          <t>World gen S3</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>BLOCKED on cat decision</t>
+          <t>Wireframe hides color; keep Pumpkin's generous silhouette. Ref: planning/reference/cats/pumpkin-orange-tabby.jpg</t>
         </is>
       </c>
     </row>

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tracker'!$A$1:$M$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tracker'!$A$1:$M$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Entry scene: S1 Hangar (chronological, recommended) or S3 Holo Stage (career-first)?</t>
+          <t>RESOLVED — Entry scene: S1 Hangar (chronological)</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -842,12 +842,12 @@
       <c r="K2" s="6" t="inlineStr"/>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>NEEDS JEFF</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>Blocks defaultSceneId + demo script.</t>
+          <t>Blocks defaultSceneId + demo script. Confirmed 2026-07-19.</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>S5 projector-wall reveal image: Jeff portrait / the three cats / logo?</t>
+          <t>RESOLVED — S5 projector-wall reveal image: Even Realities G2/R1 portrait (Louvre pyramid selfie, cropped to remove logo/text/product inset), reconstructed via bit-plane decomposition, click opens youtu.be/sEDTmvGg-QY</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -952,12 +952,12 @@
       <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>NEEDS JEFF</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>World builder votes cats. NEW candidate: the JB Proxie + all-three-cats render (planning/reference/cats/jb-proxie-with-all-three-cats.jpg) — already stylized, Matrix-green sunglasses fit Lightworks; needs grayscale conversion.</t>
+          <t>Jeff's design upgrade over the original procedural-noise plan — see TECH_SPEC.md §F. AWAITING: source image file on disk (not yet saved from chat) to run the actual bake script.</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Binary grid textures (x4) + reveal image</t>
+          <t>Baked bit-plane mask texture (reveal image)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Mint images + custom shader</t>
+          <t>custom bake script (scripts/bake-projector-image.mjs)</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>dense black and white binary square grid pattern, QR-like, flat texture (x4 masks) + 1 grayscale reveal image (PENDING Jeff decision)</t>
+          <t>Source: Jeff's Even Realities G2/R1 review portrait (Louvre pyramid), cropped to remove logo/text/product inset. Bake: downsample to 32x24 cells, quantize to 5 luminance levels, randomly assign which N-of-4 projector channels are on per cell, pack into one RGBA8 PNG (R/G/B/A = projector 0-3 bit). See TECH_SPEC.md §F.</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Additive-blend light planes summing to reveal (engineer shader).</t>
+          <t>Shader sums the 4 channels via uEnabled dot product (TECH_SPEC F); click on the resolved screen opens youtu.be/sEDTmvGg-QY.</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>Reveal image = open decision</t>
+          <t>AWAITING source image file (Jeff shared inline, not yet saved to a path I can bake from)</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC F — 4 procedural binary grids summed in one fragment shader, 5 brightness steps, beam cones, 4 manifest levers; ~11 draw calls, zero lights.</t>
+          <t>TECH_SPEC F — texture-sum fragment shader (baked bit-plane mask, Plan A) with procedural-noise fallback (Plan B) behind the same uEnabled contract, 5 brightness steps, beam cones, 4 manifest levers; ~11 draw calls, zero lights.</t>
         </is>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>Reveal-image variant needs the Mint textures instead of pure procedural — same shader slot.</t>
+          <t>Click on resolved screen opens youtu.be/sEDTmvGg-QY via the standard interaction.click handler.</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
@@ -6062,17 +6062,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>MiniGameSystem RT core (flat-disc MVP)</t>
+          <t>bake-projector-image.mjs script</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>code (5h)</t>
+          <t>code (1h)</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -6082,22 +6082,22 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>XR Engineer</t>
+          <t>Blocked on source image file</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC G — 512px RGBA8 RT at 30Hz, hard pause conditions, xr.enabled save/restore, engage mode suppressing WASD, gaze-UV steering (left/right thirds -&gt; camera CCW/CW), squeeze/pinch/W walk.</t>
+          <t>TECH_SPEC F — Node script: crop/letterbox source image, downsample to 32x24 cells, quantize to 5 luminance levels, randomly assign N-of-4 projector bits per cell (seeded), pack into one RGBA8 PNG.</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>HOUR-5 CHECKPOINT: playable on flat green disc = feature ships.</t>
+          <t>One-time offline bake, not a runtime system.</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Mini-game island + character polish</t>
+          <t>MiniGameSystem RT core (flat-disc MVP)</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>code (3-4h)</t>
+          <t>code (5h)</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -6150,17 +6150,17 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC G — island GLB &lt;=20k tris + rigged walker &lt;=10k tris (Tripo P-series 'game ready'), heightfield walk, palm sway optional.</t>
+          <t>TECH_SPEC G — 512px RGBA8 RT at 30Hz, hard pause conditions, xr.enabled save/restore, engage mode suppressing WASD, gaze-UV steering (left/right thirds -&gt; camera CCW/CW), squeeze/pinch/W walk.</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>Assets parallel-track.</t>
+          <t>HOUR-5 CHECKPOINT: playable on flat green disc = feature ships.</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Rubber-hand sequence logic</t>
+          <t>Mini-game island + character polish</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>code (2h)</t>
+          <t>code (3-4h)</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -6213,17 +6213,17 @@
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>Stroke-zone counting (N&gt;=5) -&gt; Proxie twitch anim; hammer tap -&gt; flinch+yelp; desktop click auto-stroke.</t>
+          <t>TECH_SPEC G — island GLB &lt;=20k tris + rigged walker &lt;=10k tris (Tripo P-series 'game ready'), heightfield walk, palm sway optional.</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Needs avatar anim states or mannequin-arm fallback — decide by Sat noon.</t>
+          <t>Assets parallel-track.</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
@@ -6251,17 +6251,17 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Server-repair sequence logic</t>
+          <t>Rubber-hand sequence logic</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>code (1.5h)</t>
+          <t>code (2h)</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -6281,10 +6281,14 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>3-step state machine over interactable events: sled -&gt; faulty out (cart foam) -&gt; replacement in -&gt; aisle LED ripple.</t>
-        </is>
-      </c>
-      <c r="J88" s="6" t="inlineStr"/>
+          <t>Stroke-zone counting (N&gt;=5) -&gt; Proxie twitch anim; hammer tap -&gt; flinch+yelp; desktop click auto-stroke.</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>Needs avatar anim states or mannequin-arm fallback — decide by Sat noon.</t>
+        </is>
+      </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
           <t>Interactable framework</t>
@@ -6310,17 +6314,17 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Spline-ribbon drawing</t>
+          <t>Server-repair sequence logic</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>code (2h)</t>
+          <t>code (1.5h)</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -6340,7 +6344,7 @@
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>Extruded tube along controller/cursor path, capped length, oldest fades; palette detents set color/width.</t>
+          <t>3-step state machine over interactable events: sled -&gt; faulty out (cart foam) -&gt; replacement in -&gt; aisle LED ripple.</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr"/>
@@ -6369,17 +6373,17 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Scene anim garnish (windmill sails, Chinook quarter-turn, canopy glow)</t>
+          <t>Spline-ribbon drawing</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>code (1.5h)</t>
+          <t>code (2h)</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -6394,12 +6398,12 @@
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>Simple rotation/emissive drivers via interactable effects + tiny per-role handlers.</t>
+          <t>Extruded tube along controller/cursor path, capped length, oldest fades; palette detents set color/width.</t>
         </is>
       </c>
       <c r="J90" s="6" t="inlineStr"/>
@@ -6428,12 +6432,12 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Manifest restructure to 5-scene roster + prompts.md population</t>
+          <t>Scene anim garnish (windmill sails, Chinook quarter-turn, canopy glow)</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -6448,25 +6452,25 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>XR Engineer</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>WORLD_DESIGNS roster: worlds roots/career, new sceneIds, portal graph incl. S4 cul-de-sac; migrate placards into props arrays; populate per-scene prompts.md from this tracker.</t>
-        </is>
-      </c>
-      <c r="J91" s="6" t="inlineStr">
-        <is>
-          <t>AFTER Jeff signs off the roster.</t>
-        </is>
-      </c>
-      <c r="K91" s="6" t="inlineStr"/>
+          <t>Simple rotation/emissive drivers via interactable effects + tiny per-role handlers.</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr"/>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>Interactable framework</t>
+        </is>
+      </c>
       <c r="L91" s="6" t="inlineStr">
         <is>
           <t>TODO</t>
@@ -6492,12 +6496,12 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Portal splat prefetch (fetch-only)</t>
+          <t>Manifest restructure to 5-scene roster + prompts.md population</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>code (1h)</t>
+          <t>code (1.5h)</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -6507,22 +6511,22 @@
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>XR Engineer</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC H — warm HTTP cache for entryPortals targets 3s after scene-changed; requestIdleCallback; skip on saveData.</t>
+          <t>WORLD_DESIGNS roster: worlds roots/career, new sceneIds, portal graph incl. S4 cul-de-sac; migrate placards into props arrays; populate per-scene prompts.md from this tracker.</t>
         </is>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>Stretch.</t>
+          <t>AFTER Jeff signs off the roster.</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr"/>
@@ -6551,12 +6555,12 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Quest 3 pass on deployed URL</t>
+          <t>Portal splat prefetch (fetch-only)</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>code (1h x2)</t>
+          <t>code (1h)</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -6571,15 +6575,19 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC H test matrix — TTS voices, mic absence, audio unlock, CORS origin, frame budget. End of each build block.</t>
-        </is>
-      </c>
-      <c r="J93" s="6" t="inlineStr"/>
+          <t>TECH_SPEC H — warm HTTP cache for entryPortals targets 3s after scene-changed; requestIdleCallback; skip on saveData.</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>Stretch.</t>
+        </is>
+      </c>
       <c r="K93" s="6" t="inlineStr"/>
       <c r="L93" s="6" t="inlineStr">
         <is>
@@ -6606,12 +6614,12 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Final judging rehearsal (protected)</t>
+          <t>Quest 3 pass on deployed URL</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>code (2h)</t>
+          <t>code (1h x2)</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -6631,7 +6639,7 @@
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>Full desktop + Quest walkthrough of demo script; do NOT trade for features.</t>
+          <t>TECH_SPEC H test matrix — TTS voices, mic absence, audio unlock, CORS origin, frame budget. End of each build block.</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr"/>
@@ -6643,8 +6651,63 @@
       </c>
       <c r="M94" s="6" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>T094</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>5-Code</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Final judging rehearsal (protected)</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>code (2h)</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>XR Engineer</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>Full desktop + Quest walkthrough of demo script; do NOT trade for features.</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr"/>
+      <c r="K95" s="6" t="inlineStr"/>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M94"/>
+  <autoFilter ref="A1:M95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6701,11 +6764,11 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$94,A5)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$95,A5)</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$94,A5,Tracker!$L$2:$L$94,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$95,A5,Tracker!$L$2:$L$95,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6716,11 +6779,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$94,A6)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$95,A6)</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$94,A6,Tracker!$L$2:$L$94,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$95,A6,Tracker!$L$2:$L$95,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6731,11 +6794,11 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$94,A7)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$95,A7)</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$94,A7,Tracker!$L$2:$L$94,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$95,A7,Tracker!$L$2:$L$95,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6746,11 +6809,11 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$94,A8)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$95,A8)</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$94,A8,Tracker!$L$2:$L$94,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$95,A8,Tracker!$L$2:$L$95,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6761,11 +6824,11 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$94,A9)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$95,A9)</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$94,A9,Tracker!$L$2:$L$94,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$95,A9,Tracker!$L$2:$L$95,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6776,11 +6839,11 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$94,A10)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$95,A10)</f>
         <v/>
       </c>
       <c r="C10" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$94,A10,Tracker!$L$2:$L$94,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$95,A10,Tracker!$L$2:$L$95,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6810,7 +6873,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$94,A14)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$95,A14)</f>
         <v/>
       </c>
     </row>
@@ -6821,7 +6884,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$94,A15)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$95,A15)</f>
         <v/>
       </c>
     </row>
@@ -6832,7 +6895,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$94,A16)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$95,A16)</f>
         <v/>
       </c>
     </row>
@@ -6843,7 +6906,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$94,A17)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$95,A17)</f>
         <v/>
       </c>
     </row>
@@ -6854,7 +6917,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$94,A18)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$95,A18)</f>
         <v/>
       </c>
     </row>
@@ -6865,7 +6928,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$94,A19)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$95,A19)</f>
         <v/>
       </c>
     </row>
@@ -6876,7 +6939,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$94,A20)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$95,A20)</f>
         <v/>
       </c>
     </row>
@@ -6887,7 +6950,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$94,A21)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$95,A21)</f>
         <v/>
       </c>
     </row>
@@ -6898,7 +6961,7 @@
         </is>
       </c>
       <c r="B22" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$94,A22)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$95,A22)</f>
         <v/>
       </c>
     </row>

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -979,7 +979,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Approve Proxie yelp comedy beat in rubber-hand illusion?</t>
+          <t>RESOLVED — Proxie yelp comedy beat APPROVED</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>NEEDS JEFF</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>Fallback: mannequin arm as subject, Proxie narrates.</t>
+          <t>Confirmed 2026-07-19: 'I love that comedy beat! definitely implement it' — build as speced, no mannequin-arm fallback needed.</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Pickup; tap triggers Proxie flinch+yelp (pending Jeff approval).</t>
+          <t>Pickup; tap triggers Proxie flinch+yelp (APPROVED 2026-07-19).</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>Stroke-zone counting (N&gt;=5) -&gt; Proxie twitch anim; hammer tap -&gt; flinch+yelp; desktop click auto-stroke.</t>
+          <t>Stroke-zone counting (N&gt;=5) -&gt; Proxie twitch anim; hammer tap -&gt; flinch+yelp; desktop click auto-stroke. Yelp beat APPROVED 2026-07-19.</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>Needs avatar anim states or mannequin-arm fallback — decide by Sat noon.</t>
+          <t>Needs avatar anim states (twitch/flinch) on the Proxie rig once it exists; billboard fallback = a same-named 2-frame flinch sprite swap.</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -4328,12 +4328,12 @@
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Source: Jeff's Even Realities G2/R1 review portrait (Louvre pyramid), cropped to remove logo/text/product inset. Bake: downsample to 32x24 cells, quantize to 5 luminance levels, randomly assign which N-of-4 projector channels are on per cell, pack into one RGBA8 PNG (R/G/B/A = projector 0-3 bit). See TECH_SPEC.md §F.</t>
+          <t>Source: planning/reference/cats/profileProjection.jpg (Jeff's Even Realities G2/R1 portrait, Louvre pyramid, pre-cropped). Bake: downsample to 80x80 cells (RESOLVED 2026-07-19 -- confirmed against 30/45/60/80 comparison), quantize to 5 luminance levels, randomly assign which N-of-4 projector channels are on per cell, pack into one RGBA8 PNG (R/G/B/A = projector 0-3 bit). See TECH_SPEC.md §F. Prototype validated: scripts/prototypes/bake-projector-image-prototype.py.</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Shader sums the 4 channels via uEnabled dot product (TECH_SPEC F); click on the resolved screen opens youtu.be/sEDTmvGg-QY.</t>
+          <t>Shader sums the 4 channels via uEnabled dot product (TECH_SPEC F); 4 levers toggle projectors incrementally (click/gaze/wave -- already in the interaction framework, no new plumbing); click on the resolved screen opens youtu.be/sEDTmvGg-QY.</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>AWAITING source image file (Jeff shared inline, not yet saved to a path I can bake from)</t>
+          <t>Ready to build -- only the production Node script (vs. the Python prototype) remains</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Even Realities G1 glasses</t>
+          <t>Even Realities G2 glasses</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>minimalist smart glasses with thin round frames, subtle temple modules, matte finish, game ready</t>
+          <t>minimalist smart glasses with thin rectangular frames, subtle temple modules, matte black finish, resting on a desk, game ready</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Pickup -&gt; green monochrome SIGGRAPH-guide HUD overlay; toggle off.</t>
+          <t>Pickup -&gt; green monochrome HUD overlay (real SIGGRAPH 2026 guide app branding, RESOLVED); gaze-glow affordance draws the eye (Jeff's reference render); toggle off.</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>Jeff's verbatim ask. #3 in Tripo queue</t>
+          <t>Jeff's verbatim ask + reference render received 2026-07-19. #3 in Tripo queue</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC C.2 — CSS overlay desktop / head-locked 1024x512 CanvasTexture quad XR; green phosphor SIGGRAPH schedule content; toggle off via re-click/Esc/G.</t>
+          <t>TECH_SPEC C.2 — CSS overlay desktop / head-locked 1024x512 CanvasTexture quad XR; green phosphor SIGGRAPH 2026 guide-app content -- REAL branding from Jeff's reference render (wordmark, dates, byline), not placeholder schedule copy; toggle off via re-click/Esc/G.</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC F — Node script: crop/letterbox source image, downsample to 32x24 cells, quantize to 5 luminance levels, randomly assign N-of-4 projector bits per cell (seeded), pack into one RGBA8 PNG.</t>
+          <t>TECH_SPEC F — Node port of the validated Python prototype (scripts/prototypes/bake-projector-image-prototype.py): crop/letterbox source image, downsample to 80x80 cells, quantize to 5 luminance levels, randomly assign N-of-4 projector bits per cell (seeded), pack into one RGBA8 PNG.</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -4400,7 +4400,7 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Pickup -&gt; green monochrome HUD overlay (real SIGGRAPH 2026 guide app branding, RESOLVED); gaze-glow affordance draws the eye (Jeff's reference render); toggle off.</t>
+          <t>Pickup -&gt; green monochrome HUD carousel of 5 REAL simulator screen captures (title/welcome/starred/sessions/detail, transparent PNG -- scene shows through around the UI); click left/right third of panel pages between them; gaze-glow affordance draws the eye; toggle off.</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>Jeff's verbatim ask + reference render received 2026-07-19. #3 in Tripo queue</t>
+          <t>Reference render received; 5 real screen captures pending push (planning/reference/s5-lightworks/hud-captures/). #3 in Tripo queue</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC C.2 — CSS overlay desktop / head-locked 1024x512 CanvasTexture quad XR; green phosphor SIGGRAPH 2026 guide-app content -- REAL branding from Jeff's reference render (wordmark, dates, byline), not placeholder schedule copy; toggle off via re-click/Esc/G.</t>
+          <t>TECH_SPEC C.2 -- head-locked quad (XR) / DOM overlay (desktop), texture-swap carousel across Jeff's 5 REAL simulator screen captures (transparent PNG, no invented content); click-third paging (left=prev, right=next, matches mini-game screen-third pattern); toggle off via re-click/Esc/G.</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -4400,7 +4400,7 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Pickup -&gt; green monochrome HUD carousel of 5 REAL simulator screen captures (title/welcome/starred/sessions/detail, transparent PNG -- scene shows through around the UI); click left/right third of panel pages between them; gaze-glow affordance draws the eye; toggle off.</t>
+          <t>Pickup -&gt; green monochrome HUD carousel of 9 REAL simulator screen captures (loading/welcome/starred/sessions/detail/speakers/speaker-detail/expo/expo-detail, transparent PNG -- scene shows through around the UI); click left/right third of panel pages between them; gaze-glow affordance draws the eye; toggle off.</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>READY</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>Reference render received; 5 real screen captures pending push (planning/reference/s5-lightworks/hud-captures/). #3 in Tripo queue</t>
+          <t>Reference render + all 9 real screen captures RECEIVED and committed (planning/reference/s5-lightworks/). #3 in Tripo queue -- glasses GLB itself still to generate</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>TECH_SPEC C.2 -- head-locked quad (XR) / DOM overlay (desktop), texture-swap carousel across Jeff's 5 REAL simulator screen captures (transparent PNG, no invented content); click-third paging (left=prev, right=next, matches mini-game screen-third pattern); toggle off via re-click/Esc/G.</t>
+          <t>TECH_SPEC C.2 -- head-locked quad (XR) / DOM overlay (desktop), texture-swap carousel across Jeff's 9 REAL simulator screen captures (transparent PNG, no invented content); click-third paging (left=prev, right=next, matches mini-game screen-third pattern); toggle off via re-click/Esc/G.</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>NDA pass on all S5 placard texts (drafted from public site only)</t>
+          <t>RESOLVED — NDA pass on S5 placard texts: APPROVED with one correction</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1062,12 +1062,12 @@
       <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>NEEDS JEFF</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>See WORLD_DESIGNS S5(f).</t>
+          <t>'Million-dollar hardware' line approved as dramatic license (true to how delicate/expensive the real equipment is). 'Sum wall' placard corrected: was 'bypasses the network entirely' (factually wrong) -&gt; now 'skips sequential collect-and-sum, sum appears in a single parallel glance' (Jeff's actual mechanism). GUARDRAIL: do NOT reference the Nature Communications submission anywhere in-game or on placards -- not yet public, still NDA-adjacent per Jeff 2026-07-19; site + placards stay at 'papers pending.'</t>
         </is>
       </c>
     </row>

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Drop reference photos in reference/ folders: data glove, Vive, G1 glasses, RNLAF era, Prez captures</t>
+          <t>RESOLVED — Reference photos: data glove, Tobii, mini-game island, Vive, Second Studio env RECEIVED</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1117,12 +1117,12 @@
       <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>NEEDS JEFF</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>Each strong photo converts a risky text-only generation into image-led.</t>
+          <t>planning/reference/phd research/ (dataglove uncovered.jpg -- labeled sensor diagram, unlocks jump/throw/camera-toggle mechanics not yet speced; tobii eyetracker.png; minigame environment.png -- real island screenshot: rope bridge, torii-style wooden arch, mossy hills, sand) and planning/reference/secondstudio/ (htc vive.png -- clean product shot; environment with 3D assets.png -- REAL Second Studio footage: mountain-vista platform, not the abstract wireframe void currently speced -- OPEN QUESTION back to Jeff on which direction for S4). RNLAF-era and Prez captures still welcome if he has them, not blocking.</t>
         </is>
       </c>
     </row>

--- a/planning/asset-tracker.xlsx
+++ b/planning/asset-tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tracker'!$A$1:$M$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tracker'!$A$1:$M$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Bless S4 as a Mint world generation (Path A) vs Marble (Path B)?</t>
+          <t>RESOLVED — S4 world-gen path: Marble (via Second Studio redesign to real mountain-vista platform)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1172,12 +1172,12 @@
       <c r="K8" s="6" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>NEEDS JEFF</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>Path A saves a Marble credit; pre-viz decides.</t>
+          <t>Superseded: S4 redesigned from abstract wireframe void to real mountain-vista platform per Jeff's actual Second Studio footage -- photoreal is Marble's strength, not Mint's. 42k Marble tokens confirmed loaded.</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Check Coupons &amp; Credits Notion subpage before first token spend</t>
+          <t>RESOLVED — Token pools confirmed: Mint 12k, Marble 42k, Tripo Pro (1 month)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>NEEDS JEFF</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>Per NEXT_STEPS — may add free credits.</t>
+          <t>Real numbers from Jeff directly (2026-07-19) supersede the Notion coupons-page check -- comfortably clear of the full generation budget across 5 Marble worlds + Tripo queue + Mint audio/images.</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Second Studio Construct — world</t>
+          <t>Second Studio Construct — world (REDESIGNED: mountain-vista platform, not abstract void)</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Mint (Path A) / Marble (Path B)</t>
+          <t>Marble</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>A vast stylized virtual reality workspace floating in a deep teal void, camera at standing eye height on an infinite glowing white wireframe grid floor. The horizon fades into soft cyan-to-teal gradient light, with faint aurora ribbons high above. Scattered around at chest height: abstract half-finished 3D sculptures made of glowing translucent surfaces and bright spline curves of light, frozen mid-creation. Soft cyan rim lighting on every object; gentle magenta accents on a few floating geometric primitives. No walls, no ceiling, no furniture. Palette: deep teal void, white wireframe lines, cyan glow, sparse magenta accents. The grid floor is perfectly flat and walkable in all directions for at least ten meters. Atmosphere: weightless, silent, dreamlike, clean. No photorealistic objects, no textures resembling wood or stone or concrete, no people, no text, no sky or clouds or sun, not a landscape, not outer space with stars.</t>
+          <t>A modern minimalist observation platform floating high above a dramatic snow-capped mountain range, camera at standing eye height near the platform's center. Endless jagged peaks stretch to the horizon under a bright daytime sky, soft clouds drifting in the valleys far below. The platform is a simple pale circular deck with a low glass guardrail at the edge, open to the sky and mountains on all sides -- no walls, no roof. A plain wooden work table with two simple modern chairs sits to one side, unoccupied. The deck is clean, minimal, and flat, walkable in every direction, at least eight meters across. Palette: pale platform grey, warm wood table, crisp white clouds, cool blue-grey mountain rock, bright open sky. Atmosphere: high-altitude clarity, thin drifting mist at the platform edge, quiet vastness. No people, no readable text or logos, no furniture beyond the one table and two chairs, not indoors, not nighttime, not a city skyline.</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>Generation order #2. Run parallel to S1 (different pool). Mint worlds export .spz + collider (confirmed).</t>
+          <t>REDESIGNED 2026-07-19 from Jeff's real Second Studio footage. Photoreal -&gt; Marble (was Mint/Marble Path A/B question, now resolved).</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Black biosensor data glove</t>
+          <t>Black biosensor data glove (RESOLVED art direction)</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>black fabric data glove with thin sensor strips along each finger and small circuit board on the back of the hand, wires to a connector, game ready</t>
+          <t>black fabric data glove, thin white sensor line running down the back of the middle finger and across the knuckles, small circuit board on the back of the hand, wires to a connector, game ready -- image-condition from 'planning/reference/phd research/dataglove uncovered.jpg' (labeled sensor diagram, received)</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CUT</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>Hero prop</t>
+          <t>Hero prop CUT from core scope 2026-07-19: S4 hero simplified to walking around a static skyscraper sculpture; tool-handoff/spline-drawing mechanic and its supporting props dropped. Stretch-only if time allows.</t>
         </is>
       </c>
     </row>
@@ -3630,10 +3630,14 @@
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr"/>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>CUT from core scope 2026-07-19: S4 hero simplified to walking around a static skyscraper sculpture; tool-handoff/spline-drawing mechanic and its supporting props dropped. Stretch-only if time allows.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -3693,12 +3697,12 @@
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CUT</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>Hero prop</t>
+          <t>Hero prop CUT from core scope 2026-07-19: S4 hero simplified to walking around a static skyscraper sculpture; tool-handoff/spline-drawing mechanic and its supporting props dropped. Stretch-only if time allows.</t>
         </is>
       </c>
     </row>
@@ -3760,10 +3764,14 @@
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="inlineStr"/>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>CUT from core scope 2026-07-19: S4 hero simplified to walking around a static skyscraper sculpture; tool-handoff/spline-drawing mechanic and its supporting props dropped. Stretch-only if time allows.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -3890,12 +3898,12 @@
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>CUT</t>
         </is>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>Easter egg</t>
+          <t>Easter egg CUT from core scope 2026-07-19: S4 hero simplified to walking around a static skyscraper sculpture; tool-handoff/spline-drawing mechanic and its supporting props dropped. Stretch-only if time allows.</t>
         </is>
       </c>
     </row>
@@ -3957,10 +3965,14 @@
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="M51" s="6" t="inlineStr"/>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>CUT from core scope 2026-07-19: S4 hero simplified to walking around a static skyscraper sculpture; tool-handoff/spline-drawing mechanic and its supporting props dropped. Stretch-only if time allows.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -6414,10 +6426,14 @@
       </c>
       <c r="L90" s="6" t="inlineStr">
         <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="M90" s="6" t="inlineStr"/>
+          <t>CUT</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>CUT from scope 2026-07-19 -- S4 hero simplified to a static walk-around skyscraper sculpture, no live drawing mechanic. Stretch-only.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -6706,8 +6722,138 @@
       </c>
       <c r="M95" s="6" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>T095</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>3-Prop</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Skyscraper sculpture (S4 hero, human-scale)</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Tripo</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>World Builder</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>stylized modern skyscraper architectural model, 1.8 meters tall, clean geometric facade, small rooftop details, display-quality miniature, game ready</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>Gaze-glow on approach (existing framework, no new code); walk-around only, no grab/tool mechanic.</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>World gen S4</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>NEW 2026-07-19: replaces the cut sculpting-tool/avatar-handoff hero. The walk-around centerpiece of the redesigned S4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>T096</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>5-Code</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Data-glove finger-curl animation</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>code (0.5h)</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>XR Engineer</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>2-pose blend (open &lt;-&gt; closed fist) on the glove GLB, driven by the same 0-1 flex/pinch/click-held value already computed for mini-game walk speed (TECH_SPEC G). One blend-shape or bone-rotation lerp per engaged frame, ~0.05ms.</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed by Jeff 2026-07-19: the physical glove prop should visibly perform the flex input on both platforms, not sit inert.</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>Interactable framework</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M95"/>
+  <autoFilter ref="A1:M97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6733,6 +6879,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -6764,11 +6911,11 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$95,A5)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$97,A5)</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$95,A5,Tracker!$L$2:$L$95,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$97,A5,Tracker!$L$2:$L$97,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6779,11 +6926,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$95,A6)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$97,A6)</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$95,A6,Tracker!$L$2:$L$95,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$97,A6,Tracker!$L$2:$L$97,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6794,11 +6941,11 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$95,A7)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$97,A7)</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$95,A7,Tracker!$L$2:$L$95,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$97,A7,Tracker!$L$2:$L$97,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6809,11 +6956,11 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$95,A8)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$97,A8)</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$95,A8,Tracker!$L$2:$L$95,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$97,A8,Tracker!$L$2:$L$97,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6824,11 +6971,11 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$95,A9)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$97,A9)</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$95,A9,Tracker!$L$2:$L$95,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$97,A9,Tracker!$L$2:$L$97,"DONE")</f>
         <v/>
       </c>
     </row>
@@ -6839,14 +6986,15 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTIF(Tracker!$B$2:$B$95,A10)</f>
+        <f>COUNTIF(Tracker!$B$2:$B$97,A10)</f>
         <v/>
       </c>
       <c r="C10" s="3">
-        <f>COUNTIFS(Tracker!$B$2:$B$95,A10,Tracker!$L$2:$L$95,"DONE")</f>
+        <f>COUNTIFS(Tracker!$B$2:$B$97,A10,Tracker!$L$2:$L$97,"DONE")</f>
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -6873,7 +7021,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$95,A14)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$97,A14)</f>
         <v/>
       </c>
     </row>
@@ -6884,7 +7032,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$95,A15)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$97,A15)</f>
         <v/>
       </c>
     </row>
@@ -6895,7 +7043,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$95,A16)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$97,A16)</f>
         <v/>
       </c>
     </row>
@@ -6906,7 +7054,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$95,A17)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$97,A17)</f>
         <v/>
       </c>
     </row>
@@ -6917,7 +7065,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$95,A18)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$97,A18)</f>
         <v/>
       </c>
     </row>
@@ -6928,7 +7076,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$95,A19)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$97,A19)</f>
         <v/>
       </c>
     </row>
@@ -6939,7 +7087,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$95,A20)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$97,A20)</f>
         <v/>
       </c>
     </row>
@@ -6950,7 +7098,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$95,A21)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$97,A21)</f>
         <v/>
       </c>
     </row>
@@ -6961,7 +7109,7 @@
         </is>
       </c>
       <c r="B22" s="3">
-        <f>COUNTIF(Tracker!$L$2:$L$95,A22)</f>
+        <f>COUNTIF(Tracker!$L$2:$L$97,A22)</f>
         <v/>
       </c>
     </row>
